--- a/nr-add-examples/ig/all-profiles.xlsx
+++ b/nr-add-examples/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-29T16:00:10+00:00</t>
+    <t>2025-04-30T07:38:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3926,7 +3926,7 @@
     <t>PDSm SubmissionSet Comprehensive</t>
   </si>
   <si>
-    <t>Profil spécifique dérivé du profil IHE MHD « ComprehensiveSubmissionSet » créé pour le volet ANS "Partage de documents de santé en mobilité" ; ce profil concerne le lot de soumission.</t>
+    <t>Profil du lot de soumission dérivé de la ressource List et du profil IHE MHD « ComprehensiveSubmissionSet ».</t>
   </si>
   <si>
     <t>https://profiles.ihe.net/ITI/MHD/StructureDefinition/IHE.MHD.Comprehensive.SubmissionSet</t>

--- a/nr-add-examples/ig/all-profiles.xlsx
+++ b/nr-add-examples/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-30T07:38:18+00:00</t>
+    <t>2025-04-30T07:39:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil spécifique dérivé du profil IHE MHD v4.0.1 "ComprehensiveDocumentReference" créé pour le volet "Partage de documents de santé en mobilité".</t>
+    <t>Profil contenant les métadonnées du document ainsi que le lien vers le document dérivé de la ressource DocumentReference et du profil IHE MHD v4.0.1 "ComprehensiveDocumentReference"</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/nr-add-examples/ig/all-profiles.xlsx
+++ b/nr-add-examples/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-30T07:39:59+00:00</t>
+    <t>2025-04-30T07:55:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3434,7 +3434,7 @@
     <t>PDSm Folder Comprehensive</t>
   </si>
   <si>
-    <t>Profil spécifique dérivé du profil IHE MHD « Comprehensive Folder » créé pour le volet ANS "Partage de documents de santé en mobilité" ; ce profil concerne le classeur.</t>
+    <t>Profil du Classeur dérivé de la ressource List et du profil IHE MHD « Comprehensive Folder ».</t>
   </si>
   <si>
     <t>List</t>

--- a/nr-add-examples/ig/all-profiles.xlsx
+++ b/nr-add-examples/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-30T07:55:10+00:00</t>
+    <t>2025-04-30T08:28:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -87,7 +87,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profil contenant les métadonnées du document ainsi que le lien vers le document dérivé de la ressource DocumentReference et du profil IHE MHD v4.0.1 "ComprehensiveDocumentReference"</t>
+    <t>Profil contenant les métadonnées du document ainsi que le lien vers la ressource Binary contenant le document dérivé de la ressource DocumentReference et du profil IHE MHD v4.0.1 "ComprehensiveDocumentReference"</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/nr-add-examples/ig/all-profiles.xlsx
+++ b/nr-add-examples/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-30T08:28:31+00:00</t>
+    <t>2025-04-30T11:32:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3193,7 +3193,7 @@
     <t>PDSm Find DocumentReferences Comprehensive Response</t>
   </si>
   <si>
-    <t>Profil de réponse de la transaction IHE "Find Document References [ITI-67]" basée sur le bundle MHD FindDocumentReferencesComprehensiveResponseMessage et profilé pour le volet PDSm</t>
+    <t>Profil de réponse de la transaction IHE "Find Document References [ITI-67]" basée sur le bundle MHD FindDocumentReferencesComprehensiveResponseMessage</t>
   </si>
   <si>
     <t>https://profiles.ihe.net/ITI/MHD/StructureDefinition/IHE.MHD.FindDocumentReferencesComprehensiveResponseMessage</t>
@@ -3314,7 +3314,7 @@
     <t>PDSm Find Lists Response</t>
   </si>
   <si>
-    <t>Profil de réponse de la transaction IHE "Find Document Lists [ITI-66]" basée sur le bundle MHD FindDocumentListsResponseMessage et profilé pour le volet PDSm</t>
+    <t>Profil de réponse de la transaction IHE "Find Document Lists [ITI-66]" basée sur le bundle MHD FindDocumentListsResponseMessage</t>
   </si>
   <si>
     <t>https://profiles.ihe.net/ITI/MHD/StructureDefinition/IHE.MHD.FindDocumentListsResponseMessage</t>

--- a/nr-add-examples/ig/all-profiles.xlsx
+++ b/nr-add-examples/ig/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-30T11:32:46+00:00</t>
+    <t>2025-04-30T11:36:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
